--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV_Poliakov_PRS/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV_Poliakov_PRS/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV_Poliakov_PRS\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9BA61B-FD81-43E1-8129-9387A8203900}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CC4464-8B9E-4585-AA68-8CC76FB172FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>1С</t>
   </si>
@@ -409,6 +409,9 @@
   </si>
   <si>
     <t>САН-РЕМО с/в с/н мгс 1/90 12шт.</t>
+  </si>
+  <si>
+    <t>РУБЛЕНЫЕ сос ц/о мгс 0.36кг 6шт.</t>
   </si>
 </sst>
 </file>
@@ -768,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" bestFit="1" customWidth="1"/>
@@ -2157,6 +2160,17 @@
         <v>124</v>
       </c>
     </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>1001023696765</v>
+      </c>
+      <c r="B126" s="1">
+        <v>1001023696765</v>
+      </c>
+      <c r="C126" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C120" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
